--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-13T00:30:44+00:00</t>
+          <t>2026-09-14T00:33:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14T00:33:16+00:00</t>
+          <t>2026-09-15T01:05:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15T01:05:07+00:00</t>
+          <t>2026-09-16T00:54:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-16T00:54:55+00:00</t>
+          <t>2026-09-17T02:23:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-17T02:23:21+00:00</t>
+          <t>2026-09-18T00:54:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-18T00:54:37+00:00</t>
+          <t>2026-09-19T00:49:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-19T00:49:15+00:00</t>
+          <t>2026-09-20T00:31:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-20T00:31:26+00:00</t>
+          <t>2026-09-21T00:41:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-21T00:41:29+00:00</t>
+          <t>2026-09-22T01:23:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-22T01:23:40+00:00</t>
+          <t>2026-09-23T01:04:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-23T01:04:39+00:00</t>
+          <t>2026-09-24T00:59:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-24T00:59:27+00:00</t>
+          <t>2026-09-25T01:02:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-25T01:02:36+00:00</t>
+          <t>2026-09-26T01:05:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-26T01:05:25+00:00</t>
+          <t>2026-09-27T01:02:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-27T01:02:54+00:00</t>
+          <t>2026-09-28T01:21:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28T01:21:40+00:00</t>
+          <t>2026-09-29T02:26:43+00:00</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Appointed General in the FARDC in December 2004. Handed over by the
-Government of the DRC to the International Criminal Court on 18 October 2007.  Initially convicted on 23 May 2014 by the ICC to 12 years in prison for war crimes and crimes against humanity, the ICC Appeals Chamber reduced his sentence and determined that Katanga’s sentence should be completed on 18 January 2016.  Although he was detained in the Netherlands for the duration of his trial, Katanga was transferred to a DRC prison in December 2015 and charged for other crimes previously committed in Ituri.</t>
+Government of the DRC to the International Criminal Court on 18 October 2007.  Initially convicted on 23 May 2014 by the ICC to 12 years in prison for war crimes and crimes against humanity, the ICC Appeals Chamber reduced his sentence and determined that Katanga’s sentence should be completed on 18 January 2016.  Although he was detained in the Netherlands for the duration of his trial, Katanga was transferred to a DRC prison in December 2015 and charged for other crimes previously committed in Ituri.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Arrested in Paris on 3 October 2010 under ICC warrant for war crimes and crimes against humanity committed by FDLR troops in the Kivus in 2009.  Transferred to The Hague on 25 January 2011 and released by the ICC in late 2011. Elected FDLR Executive Secretary on 29 Nov. 2014 for a five-year term.</t>
+          <t>Arrested in Paris on 3 October 2010 under ICC warrant for war crimes and crimes against humanity committed by FDLR troops in the Kivus in 2009.  Transferred to The Hague on 25 January 2011 and released by the ICC in late 2011. Elected FDLR Executive Secretary on 29 Nov. 2014 for a five-year term. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>The International Criminal Court issued an arrest warrant for Mudacumura on 12 July 2012 for nine counts of war crimes, including attacking civilians, murder, mutilation, cruel treatment, rape, torture, destruction of property, pillaging and outrages against personal dignity, allegedly committed between 2009 and 2010 in the DRC.</t>
+          <t>The International Criminal Court issued an arrest warrant for Mudacumura on 12 July 2012 for nine counts of war crimes, including attacking civilians, murder, mutilation, cruel treatment, rape, torture, destruction of property, pillaging and outrages against personal dignity, allegedly committed between 2009 and 2010 in the DRC. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Longtime member of the ADF (CDe.001), Baluku used to be the second in command to ADF founder Jamil Mukulu (CDi.015) until he took over after FARDC military operation Sukola I in 2014.</t>
+          <t>Longtime member of the ADF (CDe.001), Baluku used to be the second in command to ADF founder Jamil Mukulu (CDi.015) until he took over after FARDC military operation Sukola I in 2014.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -2123,7 +2123,7 @@
       <c r="F38" s="5" t="inlineStr"/>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraphs 7 (b), 7 (e), and 7 (h) of resolution 2293 (2016) as “being political and military leaders of foreign armed groups operating in the DRC who impede the disarmament and the voluntary repatriation or resettlement of combatants belonging to those groups”; “committing acts in the DRC that constitute human rights violations or abuses or violations of international humanitarian law, as applicable, including those acts involving the targeting of civilians, including killing and maiming, rape and other sexual violence, abduction, forced displacement, and attacks on schools and hospitals”; and “acting on behalf of or at the direction of a designated individual or entity, or acting on behalf of or at the direction of an entity owned or controlled by a designated individual or entity”, as reaffirmed by paragraph 2 of resolution 2688 (2023). As a leader of FDLR (CDe.005), he has effective command and control over the group’s combatants.</t>
+          <t>Listed pursuant to paragraphs 7 (b), 7 (e), and 7 (h) of resolution 2293 (2016) as “being political and military leaders of foreign armed groups operating in the DRC who impede the disarmament and the voluntary repatriation or resettlement of combatants belonging to those groups”; “committing acts in the DRC that constitute human rights violations or abuses or violations of international humanitarian law, as applicable, including those acts involving the targeting of civilians, including killing and maiming, rape and other sexual violence, abduction, forced displacement, and attacks on schools and hospitals”; and “acting on behalf of or at the direction of a designated individual or entity, or acting on behalf of or at the direction of an entity owned or controlled by a designated individual or entity”, as reaffirmed by paragraph 2 of resolution 2688 (2023). As a leader of FDLR (CDe.005), he has effective command and control over the group’s combatants.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraphs 7 (c) and 7 (h) of resolution 2293 (2016) as “political and military leaders of Congolese militias, including those receiving support from outside the DRC, who impede the participation of their combatants in disarmament, demobilization and reintegration processes”; and “acting on behalf of or at the direction of a designated individual or entity, or acting on behalf of or at the direction of an entity owned or controlled by a designated individual or entity”, as reaffirmed by paragraph 2 of resolution 2688 (2023). As a leader of M23 (CDe.006), he is involved in promulgating and supporting the armed group’s activities. He was promoted in January 2023 to Brigadier for the Congolese Revolutionary Army, the M23 armed branch. He was then appointed chief of staff and deputy to SULTANI MAKENGA (CDi.008), and has validated the planning for every M23 operations in DRC since then. A warrant has been issued by Congolese authorities for his arrest.</t>
+          <t>Listed pursuant to paragraphs 7 (c) and 7 (h) of resolution 2293 (2016) as “political and military leaders of Congolese militias, including those receiving support from outside the DRC, who impede the participation of their combatants in disarmament, demobilization and reintegration processes”; and “acting on behalf of or at the direction of a designated individual or entity, or acting on behalf of or at the direction of an entity owned or controlled by a designated individual or entity”, as reaffirmed by paragraph 2 of resolution 2688 (2023). As a leader of M23 (CDe.006), he is involved in promulgating and supporting the armed group’s activities. He was promoted in January 2023 to Brigadier for the Congolese Revolutionary Army, the M23 armed branch. He was then appointed chief of staff and deputy to SULTANI MAKENGA (CDi.008), and has validated the planning for every M23 operations in DRC since then. A warrant has been issued by Congolese authorities for his arrest.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraphs 7 (b), 7 (e) and 7 (h) of resolution 2293 (2016) as “being political and military leaders of foreign armed groups operating in the DRC who impede the disarmament and the voluntary repatriation or resettlement of combatants belonging to those groups”; “planning, directing, or committing acts in the DRC that constitute human rights violations or abuses or violations of international humanitarian law, as applicable, including those acts involving the targeting of civilians, including killing and maiming, rape and other sexual violence, abduction, forced displacement, and attacks on schools and hospitals”; and “acting on behalf of or at the direction of a designated individual or entity, or acting on behalf of or at the direction of an entity owned or controlled by a designated individual or entity,” as extended by resolution 2688 (2023). As a military leader of FDLR, APOLLINAIRE HAKIZIMANA is involved in promulgating and supporting the group’s activities.</t>
+          <t>Listed pursuant to paragraphs 7 (b), 7 (e) and 7 (h) of resolution 2293 (2016) as “being political and military leaders of foreign armed groups operating in the DRC who impede the disarmament and the voluntary repatriation or resettlement of combatants belonging to those groups”; “planning, directing, or committing acts in the DRC that constitute human rights violations or abuses or violations of international humanitarian law, as applicable, including those acts involving the targeting of civilians, including killing and maiming, rape and other sexual violence, abduction, forced displacement, and attacks on schools and hospitals”; and “acting on behalf of or at the direction of a designated individual or entity, or acting on behalf of or at the direction of an entity owned or controlled by a designated individual or entity,” as extended by resolution 2688 (2023). As a military leader of FDLR, APOLLINAIRE HAKIZIMANA is involved in promulgating and supporting the group’s activities. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraphs 7 (b), 7 (e), and 7 (h) of resolution 2293 (2016) and paragraph 3 of resolution 2641 (2022): “being political and military leaders of foreign armed groups operating in the DRC who impede the disarmament and the voluntary repatriation or resettlement of combatants belonging to those groups”, “planning, directing, or committing acts in the DRC that constitute human rights violations or abuses or violations of international humanitarian law, as applicable, including those acts involving the targeting of civilians, including killing and maiming, rape and other sexual violence, abduction, forced displacement, and attacks on schools and hospitals”, “acting on behalf of or at the direction of a designated individual or entity, or acting on behalf of or at the direction of an entity owned or controlled by a designated individual or entity”, and “involve[d] in the production, manufacture or use in the DRC of improvised explosive devices, or in the commission, planning, ordering, aiding, abetting or otherwise assistance of attacks in the DRC with improvised explosive devices”.</t>
+          <t>Listed pursuant to paragraphs 7 (b), 7 (e), and 7 (h) of resolution 2293 (2016) and paragraph 3 of resolution 2641 (2022): “being political and military leaders of foreign armed groups operating in the DRC who impede the disarmament and the voluntary repatriation or resettlement of combatants belonging to those groups”, “planning, directing, or committing acts in the DRC that constitute human rights violations or abuses or violations of international humanitarian law, as applicable, including those acts involving the targeting of civilians, including killing and maiming, rape and other sexual violence, abduction, forced displacement, and attacks on schools and hospitals”, “acting on behalf of or at the direction of a designated individual or entity, or acting on behalf of or at the direction of an entity owned or controlled by a designated individual or entity”, and “involve[d] in the production, manufacture or use in the DRC of improvised explosive devices, or in the commission, planning, ordering, aiding, abetting or otherwise assistance of attacks in the DRC with improvised explosive devices”. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraph 7 (c), 7 (d), and 7 (e) of resolution 2293 (2016) as “being political and military leaders of Congolese militias, including those receiving support from outside the DRC, who impede the participation of their combatants in disarmament, demobilization and reintegration processes”; “recruiting or using children in armed conflict in the DRC in violation of applicable international law”; “planning, directing, or committing acts in the DRC that constitute human rights violations or abuses or violations of international humanitarian law, as applicable, including those acts involving the targeting of civilians, including killing and maiming, rape and other sexual violence, abduction, forced displacement, and attacks on schools and hospitals” and “acting on behalf of or at the direction of a designated individual or entity, or acting on behalf of or at the direction of an entity owned or controlled by a designated individual or entity”, as extended by resolution 2688 (2023). As a military leader of an armed Congolese militia, MICHEL RUKUNDA is involved in promulgating and supporting the group’s activities.</t>
+          <t>Listed pursuant to paragraph 7 (c), 7 (d), and 7 (e) of resolution 2293 (2016) as “being political and military leaders of Congolese militias, including those receiving support from outside the DRC, who impede the participation of their combatants in disarmament, demobilization and reintegration processes”; “recruiting or using children in armed conflict in the DRC in violation of applicable international law”; “planning, directing, or committing acts in the DRC that constitute human rights violations or abuses or violations of international humanitarian law, as applicable, including those acts involving the targeting of civilians, including killing and maiming, rape and other sexual violence, abduction, forced displacement, and attacks on schools and hospitals” and “acting on behalf of or at the direction of a designated individual or entity, or acting on behalf of or at the direction of an entity owned or controlled by a designated individual or entity”, as extended by resolution 2688 (2023). As a military leader of an armed Congolese militia, MICHEL RUKUNDA is involved in promulgating and supporting the group’s activities.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -2333,7 +2333,8 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraphs 7 (b), 7 (d), 7 (e), and 7 (h) of resolution 2293 (2016) as “being political and military leaders of foreign armed groups operating in the DRC who impede the disarmament and the voluntary repatriation or resettlement of combatants belonging to those groups; “recruiting or using children in armed conflict in the DRC in violation of applicable international law; “planning, directing, committing acts in the DRC that constitute human rights violations or abuses or violations of international humanitarian law, as applicable, including those acts involving the targeting of civilians, including killing and maiming, rape and other sexual violence, abduction, forced displacement, and attacks on schools and hospitals”; and “acting on behalf of or at the direction of a designated individual or entity, or acting on behalf of or at the direction of an entity owned or controlled by a designated individual or entity”, as reaffirmed by paragraph 2 of resolution 2688 (2023). As a leader of ADF (CDe.001), MOHAMED ALI NKALUBO is involved in planning, promulgating and supporting the armed group’s activities. He has effective command and control over the group’s combatants.</t>
+          <t>Listed pursuant to paragraphs 7 (b), 7 (d), 7 (e), and 7 (h) of resolution 2293 (2016) as “being political and military leaders of foreign armed groups operating in the DRC who impede the disarmament and the voluntary repatriation or resettlement of combatants belonging to those groups; “recruiting or using children in armed conflict in the DRC in violation of applicable international law; “planning, directing, committing acts in the DRC that constitute human rights violations or abuses or violations of international humanitarian law, as applicable, including those acts involving the targeting of civilians, including killing and maiming, rape and other sexual violence, abduction, forced displacement, and attacks on schools and hospitals”; and “acting on behalf of or at the direction of a designated individual or entity, or acting on behalf of or at the direction of an entity owned or controlled by a designated individual or entity”, as reaffirmed by paragraph 2 of resolution 2688 (2023). As a leader of ADF (CDe.001), MOHAMED ALI NKALUBO is involved in planning, promulgating and supporting the armed group’s activities. He has effective command and control over the group’s combatants. 
+ INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -2375,7 +2376,7 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraphs 7 (c), 7 (d), 7 (e) and 7 (g) of resolution 2293 (2016) as “being political and military leaders of Congolese militias, including those receiving support from outside the DRC, who impede the participation of their combatants in disarmament, demobilization and reintegration processes;” “recruiting or using children in armed conflict in the DRC in violation of applicable international law;” “planning, directing, committing acts in the DRC that constitute human rights violations or abuses or violations of international humanitarian law, as applicable, including those acts involving the targeting of civilians, including killing and maiming, rape and other sexual violence, abduction, forced displacement, and attacks on schools and hospitals;” and “supporting individuals or entities, including armed groups or criminal networks, involved in destabilizing activities in the DRC through the illicit exploitation or trade of natural resources, including gold or wildlife as well as wildlife products”, as reaffirmed by paragraph 2 of resolution 2688 (2023). As the leader of the MAI MAI YAKUTUMBA, one of the largest CNPSC militia, WILLIAM AMURI YAKUTUMBA is involved in planning, promulgating and supporting the militia’s activities. He has effective command and control over the militia’s combatants.</t>
+          <t>Listed pursuant to paragraphs 7 (c), 7 (d), 7 (e) and 7 (g) of resolution 2293 (2016) as “being political and military leaders of Congolese militias, including those receiving support from outside the DRC, who impede the participation of their combatants in disarmament, demobilization and reintegration processes;” “recruiting or using children in armed conflict in the DRC in violation of applicable international law;” “planning, directing, committing acts in the DRC that constitute human rights violations or abuses or violations of international humanitarian law, as applicable, including those acts involving the targeting of civilians, including killing and maiming, rape and other sexual violence, abduction, forced displacement, and attacks on schools and hospitals;” and “supporting individuals or entities, including armed groups or criminal networks, involved in destabilizing activities in the DRC through the illicit exploitation or trade of natural resources, including gold or wildlife as well as wildlife products”, as reaffirmed by paragraph 2 of resolution 2688 (2023). As the leader of the MAI MAI YAKUTUMBA, one of the largest CNPSC militia, WILLIAM AMURI YAKUTUMBA is involved in planning, promulgating and supporting the militia’s activities. He has effective command and control over the militia’s combatants.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -2413,7 +2414,8 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraphs 7 (c), 7 (e) and 7 (h) of resolution 2293 (2016) as “being political and military leaders of Congolese militias, including those receiving support from outside the DRC, who impede the participation of their combatants in disarmament, demobilization and reintegration processes;” “planning, directing, committing acts in the DRC that constitute human rights violations or abuses or violations of international humanitarian law, as applicable, including those acts involving the targeting of civilians, including killing and maiming, rape and other sexual violence, abduction, forced displacement, and attacks on schools and hospitals;” and “acting on behalf of or at the direction of an entity owned or controlled by a designated individual or entity”, as reaffirmed by paragraph 2 of resolution 2688 (2023). As a leader of M23 (CDe.006), WILLY NGOMA is involved in planning, promulgating and supporting the armed group’s activities.</t>
+          <t>Listed pursuant to paragraphs 7 (c), 7 (e) and 7 (h) of resolution 2293 (2016) as “being political and military leaders of Congolese militias, including those receiving support from outside the DRC, who impede the participation of their combatants in disarmament, demobilization and reintegration processes;” “planning, directing, committing acts in the DRC that constitute human rights violations or abuses or violations of international humanitarian law, as applicable, including those acts involving the targeting of civilians, including killing and maiming, rape and other sexual violence, abduction, forced displacement, and attacks on schools and hospitals;” and “acting on behalf of or at the direction of an entity owned or controlled by a designated individual or entity”, as reaffirmed by paragraph 2 of resolution 2688 (2023). As a leader of M23 (CDe.006), WILLY NGOMA is involved in planning, promulgating and supporting the armed group’s activities.
+ INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -3164,7 +3166,7 @@
 was in Brazzaville before returning to the CAR (between November 2014 and 2019). The FDPC
 signed the Political Agreement for Peace and Reconciliation in the CAR on 6 February 2019 but
 Martin Koumtamadji remains a threat to the peace, stability and security of the CAR. Photo available
-for inclusion in the INTERPOL-UN Security Council Special Notice.</t>
+for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
@@ -11905,7 +11907,7 @@
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban, Asset Freeze)</t>
+          <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban, Asset Freeze) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H292" s="5" t="inlineStr">
@@ -11947,7 +11949,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban, Asset Freeze)</t>
+          <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban, Asset Freeze) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -11989,7 +11991,7 @@
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban, Asset Freeze)</t>
+          <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban, Asset Freeze) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H294" s="5" t="inlineStr">
@@ -12031,7 +12033,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban, Asset Freeze)</t>
+          <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban, Asset Freeze) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -12073,7 +12075,7 @@
       </c>
       <c r="G296" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban, Asset Freeze)</t>
+          <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban, Asset Freeze) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H296" s="5" t="inlineStr">
@@ -12115,7 +12117,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban, Asset Freeze),  1) Name of mother Huriyah Al-A’ib; and 2) Military ID is 36479</t>
+          <t>Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban, Asset Freeze),  1) Name of mother Huriyah Al-A’ib; and 2) Military ID is 36479  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -12157,7 +12159,7 @@
       </c>
       <c r="G298" s="5" t="inlineStr">
         <is>
-          <t>Name of mother Salma Abdula Younis. Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban, Asset Freeze).</t>
+          <t>Name of mother Salma Abdula Younis. Listed pursuant to paragraphs 15 and 17 of resolution 1970 (Travel Ban, Asset Freeze).   INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H298" s="5" t="inlineStr">
@@ -12275,7 +12277,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>Responsible for Usama bin Laden’s (deceased) security. Hair: Dark. Eyes: Dark. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-312380</t>
+          <t>Responsible for Usama bin Laden’s (deceased) security. Hair: Dark. Eyes: Dark. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -12317,7 +12319,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>Security coordinator for Usama bin Laden (deceased). Repatriated to Afghanistan in February 2006. He was in Afghanistan as of August 2021. Arrested in Pakistan 2024 and deported to Afghanistan in 2025. Father’s name: Abdul Rahman. Photo and fingerprints available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-21201</t>
+          <t>Security coordinator for Usama bin Laden (deceased). Repatriated to Afghanistan in February 2006. He was in Afghanistan as of August 2021. Arrested in Pakistan 2024 and deported to Afghanistan in 2025. Father’s name: Abdul Rahman. Photo and fingerprints available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -12355,7 +12357,7 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>Driver and private bodyguard to Usama bin Laden (deceased) from 1996 until 2001. Transferred from United States custody to Yemen in Nov. 2008</t>
+          <t>Driver and private bodyguard to Usama bin Laden (deceased) from 1996 until 2001. Transferred from United States custody to Yemen in Nov. 2008 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
@@ -13771,7 +13773,7 @@
       </c>
       <c r="G337" s="5" t="inlineStr">
         <is>
-          <t>Senior leader of Jemaah Islamiyah (QDe.092). Brother of Gun Gun Rusman Gunawan (QDi.218). In custody of the United States of America, as of July 2007 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2002-40158</t>
+          <t>Senior leader of Jemaah Islamiyah (QDe.092). Brother of Gun Gun Rusman Gunawan (QDi.218). In custody of the United States of America, as of July 2007 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H337" s="5" t="inlineStr">
@@ -13935,7 +13937,7 @@
       </c>
       <c r="G341" s="5" t="inlineStr">
         <is>
-          <t>A member of the Abu Sayyaf Group (QDe.001). In detention in the Philippines as at May 2011 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-22291</t>
+          <t>A member of the Abu Sayyaf Group (QDe.001). In detention in the Philippines as at May 2011 INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H341" s="5" t="inlineStr">
@@ -15393,7 +15395,7 @@
       </c>
       <c r="G376" s="5" t="inlineStr">
         <is>
-          <t>Senior leader of Abu Sayyaf Group (ASG) (QDe.001). Leader of local affiliates of the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (AQI) (QDe.115), in the southern Philippines as of May 2017. Killed in Marawi City, Philippines on 15 October 2017. Physical description: eye colour: brown; hair colour: brown; height: 5 feet 6 inches – 168 cm; weight: 120 pounds – 54 kg; build: slim; complexion: light-skinned; has facial birthmarks. Wanted by the Philippines authorities for terrorist offences and by authorities of the United States of America for involvement in terrorist acts. Photos included in INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2016-35239</t>
+          <t>Senior leader of Abu Sayyaf Group (ASG) (QDe.001). Leader of local affiliates of the Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (AQI) (QDe.115), in the southern Philippines as of May 2017. Killed in Marawi City, Philippines on 15 October 2017. Physical description: eye colour: brown; hair colour: brown; height: 5 feet 6 inches – 168 cm; weight: 120 pounds – 54 kg; build: slim; complexion: light-skinned; has facial birthmarks. Wanted by the Philippines authorities for terrorist offences and by authorities of the United States of America for involvement in terrorist acts. Photos included in INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H376" s="5" t="inlineStr">
@@ -16401,7 +16403,7 @@
       </c>
       <c r="G400" s="5" t="inlineStr">
         <is>
-          <t>Located in Northern Mali as of Jun. 2008. Reportedly killed on 25 February 2022 in Timbuktu, Mali. Belonged to the leadership of the Organization of Al-Qaida in the Islamic Maghreb (listed under permanent reference number QDe.014). Mother’s name is Zohra Fares. Father’s name is Mohamed. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2003-33116</t>
+          <t>Located in Northern Mali as of Jun. 2008. Reportedly killed on 25 February 2022 in Timbuktu, Mali. Belonged to the leadership of the Organization of Al-Qaida in the Islamic Maghreb (listed under permanent reference number QDe.014). Mother’s name is Zohra Fares. Father’s name is Mohamed. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H400" s="5" t="inlineStr">
@@ -16527,7 +16529,7 @@
       </c>
       <c r="G403" s="5" t="inlineStr">
         <is>
-          <t>Belongs to the leadership and is the finance chief of the Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Mother’s name is Zakia Chebira. Father’s name is Lakhdar. Reportedly died in Algeria in 2020. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2008-27768</t>
+          <t>Belongs to the leadership and is the finance chief of the Organization of Al-Qaida in the Islamic Maghreb (QDe.014). Mother’s name is Zakia Chebira. Father’s name is Lakhdar. Reportedly died in Algeria in 2020. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H403" s="5" t="inlineStr">
@@ -16569,7 +16571,7 @@
       </c>
       <c r="G404" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Islamic Jihad Union (IJU), also known as the Islamic Jihad Group (QDe.119). Deported from Germany to Türkiye in February 2019. Ongoing judicial process as of November 2023. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-44887</t>
+          <t>Associated with the Islamic Jihad Union (IJU), also known as the Islamic Jihad Group (QDe.119). Deported from Germany to Türkiye in February 2019. Ongoing judicial process as of November 2023. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H404" s="5" t="inlineStr">
@@ -17359,7 +17361,7 @@
       </c>
       <c r="G423" s="5" t="inlineStr">
         <is>
-          <t>Operative and principal bomb maker of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Reportedly deceased in 2017. Also associated with Nasir 'abd-al-Karim 'Abdullah Al-Wahishi (deceased), Qasim Yahya Mahdi al-Rimi (QDi.282), and Anwar Nasser Abdulla Al-Aulaqi (QDi.283) (deceased). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-3367</t>
+          <t>Operative and principal bomb maker of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Reportedly deceased in 2017. Also associated with Nasir 'abd-al-Karim 'Abdullah Al-Wahishi (deceased), Qasim Yahya Mahdi al-Rimi (QDi.282), and Anwar Nasser Abdulla Al-Aulaqi (QDi.283) (deceased). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H423" s="5" t="inlineStr">
@@ -17485,7 +17487,7 @@
       </c>
       <c r="G426" s="5" t="inlineStr">
         <is>
-          <t>Senior member of Jemaah Islamiyah (QDe.092) involved in planning and funding multiple terrorist attacks in the Philippines and Indonesia. Provided training to Abu Sayyaf Group (QDe.001). Convicted for his role in the 2002 Bali bombings and sentenced to 20 years in prison in Jun. 2012. Released on parole in 2022 and as at late 2025, he operated a business in Surabaya, Indonesia. Photos included in  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-3367</t>
+          <t>Senior member of Jemaah Islamiyah (QDe.092) involved in planning and funding multiple terrorist attacks in the Philippines and Indonesia. Provided training to Abu Sayyaf Group (QDe.001). Convicted for his role in the 2002 Bali bombings and sentenced to 20 years in prison in Jun. 2012. Released on parole in 2022 and as at late 2025, he operated a business in Surabaya, Indonesia. Photos included in  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H426" s="5" t="inlineStr">
@@ -17527,7 +17529,7 @@
       </c>
       <c r="G427" s="5" t="inlineStr">
         <is>
-          <t>Senior member of Jemaah Islamiyah (QDe.092) directly involved in obtaining funding for terrorist attacks. Sentenced in Indonesia to five years in prison on 29 Jun. 2010. Father’s name is Mohamad Iqbal Abdurrahman (QDi.086). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-290638</t>
+          <t>Senior member of Jemaah Islamiyah (QDe.092) directly involved in obtaining funding for terrorist attacks. Sentenced in Indonesia to five years in prison on 29 Jun. 2010. Father’s name is Mohamad Iqbal Abdurrahman (QDi.086). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H427" s="5" t="inlineStr">
@@ -17695,7 +17697,7 @@
       </c>
       <c r="G431" s="5" t="inlineStr">
         <is>
-          <t>Associated with Islamic Movement of Uzbekistan (QDe.010). Associated with Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), between October 2015 and August 2016. Brother of Yassin Chouka (QDi.301). Arrest warrant issued by the investigating judge of the German Federal Court of Justice on 5 Oct. 2010. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-290688</t>
+          <t>Associated with Islamic Movement of Uzbekistan (QDe.010). Associated with Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115), between October 2015 and August 2016. Brother of Yassin Chouka (QDi.301). Arrest warrant issued by the investigating judge of the German Federal Court of Justice on 5 Oct. 2010. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H431" s="5" t="inlineStr">
@@ -17821,7 +17823,7 @@
       </c>
       <c r="G434" s="5" t="inlineStr">
         <is>
-          <t>Acting emir of Jemmah Anshorut Tauhid (JAT) (QDe.133). Associated with Abu Bakar Ba’asyir (QDi.217), Abdul Rahim Ba’aysir (QDi.293) and Jemaah Islamiyah (QDe.092). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-312423</t>
+          <t>Acting emir of Jemmah Anshorut Tauhid (JAT) (QDe.133). Associated with Abu Bakar Ba’asyir (QDi.217), Abdul Rahim Ba’aysir (QDi.293) and Jemaah Islamiyah (QDe.092). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H434" s="5" t="inlineStr">
@@ -18909,7 +18911,7 @@
       </c>
       <c r="G460" s="5" t="inlineStr">
         <is>
-          <t>Fundraiser for Al-Nusrah Front for the People of the Levant (formerly listed). In November 2023, he was released from prison in Kuwait as part of the Special Amiri Decree Pardon No. 225/2023. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2014-58611</t>
+          <t>Fundraiser for Al-Nusrah Front for the People of the Levant (formerly listed). In November 2023, he was released from prison in Kuwait as part of the Special Amiri Decree Pardon No. 225/2023. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H460" s="5" t="inlineStr">
@@ -20195,7 +20197,7 @@
       </c>
       <c r="G491" s="5" t="inlineStr">
         <is>
-          <t>French-Tunisian foreign terrorist fighter for Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Reportedly killed in Raqqa, Syria on 26 November 2016. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2015-64575</t>
+          <t>French-Tunisian foreign terrorist fighter for Islamic State in Iraq and the Levant (ISIL), listed as Al-Qaida in Iraq (QDe.115). Reportedly killed in Raqqa, Syria on 26 November 2016. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H491" s="5" t="inlineStr">
@@ -20233,7 +20235,7 @@
       </c>
       <c r="G492" s="5" t="inlineStr">
         <is>
-          <t>Member of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Convicted in absentia to five years in prison in France in 2012. Wanted by French authorities as of 2015. Sentenced to life imprisonment by a French court on 3 October 2024.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2015-64577</t>
+          <t>Member of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Convicted in absentia to five years in prison in France in 2012. Wanted by French authorities as of 2015. Sentenced to life imprisonment by a French court on 3 October 2024.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H492" s="5" t="inlineStr">
@@ -20691,7 +20693,7 @@
       </c>
       <c r="G503" s="5" t="inlineStr">
         <is>
-          <t>A leader of the Organization of Al-Qaida in the Islamic Maghreb (AQIM) (QDe.014). Father’s name is Omar Mebrak. Mother’s name is Zohra Mebrak. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2016-13643</t>
+          <t>A leader of the Organization of Al-Qaida in the Islamic Maghreb (AQIM) (QDe.014). Father’s name is Omar Mebrak. Mother’s name is Zohra Mebrak. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H503" s="5" t="inlineStr">
@@ -22355,7 +22357,7 @@
       </c>
       <c r="G543" s="5" t="inlineStr">
         <is>
-          <t>Senior leader of the Islamic State in Iraq and the Levant - Khorasan (ISIL - K) (QDe.161)</t>
+          <t>Senior leader of the Islamic State in Iraq and the Levant - Khorasan (ISIL - K) (QDe.161) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H543" s="5" t="inlineStr">
@@ -22431,7 +22433,7 @@
       </c>
       <c r="G545" s="5" t="inlineStr">
         <is>
-          <t>Abubakar Swalleh provides financial, material, or technological support for, or financial or other services to, or in support of, ISIL (listed as Al-Qaida in Iraq (QDe.115)). He acted, since 2018, as an ISIL facilitator who provides financial and logistic support including recruitment for ISIL in East and Southern Africa. Phone number: +963936016952. Gender: Male. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2025-47413</t>
+          <t>Abubakar Swalleh provides financial, material, or technological support for, or financial or other services to, or in support of, ISIL (listed as Al-Qaida in Iraq (QDe.115)). He acted, since 2018, as an ISIL facilitator who provides financial and logistic support including recruitment for ISIL in East and Southern Africa. Phone number: +963936016952. Gender: Male. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H545" s="5" t="inlineStr">
@@ -22473,7 +22475,7 @@
       </c>
       <c r="G546" s="5" t="inlineStr">
         <is>
-          <t>Assumed multiples roles within ISIL (Da’esh) listed as Al-Qaida in Iraq (QDe.115), including overseeing ISIL’s finances, material affairs and sources of revenue. He was also a member of the so-called Delegated Committee, which is the decision-making body of ISIL (Da’esh). He also participated in several terrorist operations against security forces while ISIL was controlling territory and was involved in the smuggling of oil derivates. Mother’s name: A’ishah Hasan. Gender: Male, Physical description: eye colour: black; hair colour: black; Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:</t>
+          <t>Assumed multiples roles within ISIL (Da’esh) listed as Al-Qaida in Iraq (QDe.115), including overseeing ISIL’s finances, material affairs and sources of revenue. He was also a member of the so-called Delegated Committee, which is the decision-making body of ISIL (Da’esh). He also participated in several terrorist operations against security forces while ISIL was controlling territory and was involved in the smuggling of oil derivates. Mother’s name: A’ishah Hasan. Gender: Male, Physical description: eye colour: black; hair colour: black; Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H546" s="5" t="inlineStr">
@@ -22515,7 +22517,7 @@
       </c>
       <c r="G547" s="5" t="inlineStr">
         <is>
-          <t>Served as a senior leader in ISIL (Da’esh) listed as Al-Qaida in Iraq (QDe.115) as its financial management officer. Mother’s name: Khadija Hattab Ismail. Gender: Male INTERPOL-UN Security Council Special Notice:</t>
+          <t>Served as a senior leader in ISIL (Da’esh) listed as Al-Qaida in Iraq (QDe.115) as its financial management officer. Mother’s name: Khadija Hattab Ismail. Gender: Male INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H547" s="5" t="inlineStr">
@@ -22557,7 +22559,7 @@
       </c>
       <c r="G548" s="5" t="inlineStr">
         <is>
-          <t>Works as a mediator in financing channels for ISIL in Central Africa, has been charged with financing a bombing that occurred in the Ugandan capital, Kampala, in 2021, attempted to coerce her three children in Uganda to send them to ISIL camps in the Democratic Republic of the Congo. Gender: Female. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2026-23487</t>
+          <t>Works as a mediator in financing channels for ISIL in Central Africa, has been charged with financing a bombing that occurred in the Ugandan capital, Kampala, in 2021, attempted to coerce her three children in Uganda to send them to ISIL camps in the Democratic Republic of the Congo. Gender: Female. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H548" s="5" t="inlineStr">
@@ -22721,7 +22723,7 @@
       </c>
       <c r="G552" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male.</t>
+          <t>Gender: Male.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H552" s="5" t="inlineStr">
@@ -22759,7 +22761,7 @@
       </c>
       <c r="G553" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male.</t>
+          <t>Gender: Male. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H553" s="5" t="inlineStr">
@@ -22839,7 +22841,7 @@
       </c>
       <c r="G555" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male. INTERPOL-UN Security Council Special Notice:</t>
+          <t>Gender: Male. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H555" s="5" t="inlineStr">
@@ -23929,7 +23931,8 @@
         <is>
           <t>Gender: Male. Listed pursuant to paragraph 26(b) of resolution 2662 (2022): (i) participating in the financing, planning, facilitating, preparing, or perpetrating of acts or activities by, in conjunction with, under the name of, on behalf of, or in support of Al-Shabaab and
 (iii) recruiting for, or otherwise supporting acts or activities of Al-Shabaab or any cell, affiliate,
-splinter group or derivative thereof.</t>
+splinter group or derivative thereof.
+ INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H582" s="5" t="inlineStr">
@@ -23971,7 +23974,7 @@
       </c>
       <c r="G583" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male. Listed pursuant to paragraph 26 of resolution 2662 (2022): (a) having engaged in, or provided support for, acts that threatened the peace, security or stability of Somalia, including acts that threatened the peace and reconciliation process in Somalia, or threatened the Federal Government of Somalia or ATMIS by force; and (b)(i) participating in the financing, planning, facilitating, preparing, or perpetrating of acts or activities by, in conjunction with, under the name of, on behalf of, or in support of Al-Shabaab.</t>
+          <t>Gender: Male. Listed pursuant to paragraph 26 of resolution 2662 (2022): (a) having engaged in, or provided support for, acts that threatened the peace, security or stability of Somalia, including acts that threatened the peace and reconciliation process in Somalia, or threatened the Federal Government of Somalia or ATMIS by force; and (b)(i) participating in the financing, planning, facilitating, preparing, or perpetrating of acts or activities by, in conjunction with, under the name of, on behalf of, or in support of Al-Shabaab.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H583" s="5" t="inlineStr">
@@ -24009,7 +24012,7 @@
       <c r="F584" s="5" t="inlineStr"/>
       <c r="G584" s="5" t="inlineStr">
         <is>
-          <t>Gender: Male. Listed pursuant to paragraph 26(b) of resolution 2662 (2022): (i) participating in the financing, planning, facilitating, preparing, or perpetrating of acts or activities by, in conjunction with, under the name of, on behalf of, or in support of Al-Shabaab; and (iii) recruiting for, or otherwise supporting acts or activities of Al-Shabaab or any cell, affiliate, splinter group or derivative thereof.</t>
+          <t>Gender: Male. Listed pursuant to paragraph 26(b) of resolution 2662 (2022): (i) participating in the financing, planning, facilitating, preparing, or perpetrating of acts or activities by, in conjunction with, under the name of, on behalf of, or in support of Al-Shabaab; and (iii) recruiting for, or otherwise supporting acts or activities of Al-Shabaab or any cell, affiliate, splinter group or derivative thereof.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H584" s="5" t="inlineStr">
@@ -24307,7 +24310,7 @@
       </c>
       <c r="G591" s="5" t="inlineStr">
         <is>
-          <t>As SPLA Deputy Chief of Staff for Logistics, Riak was one of the senior officials of the Government of South Sudan who planned and oversaw an offensive in Unity state in 2015 that resulted in widespread destruction and large population displacement.</t>
+          <t>As SPLA Deputy Chief of Staff for Logistics, Riak was one of the senior officials of the Government of South Sudan who planned and oversaw an offensive in Unity state in 2015 that resulted in widespread destruction and large population displacement.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H591" s="5" t="inlineStr">
@@ -24349,7 +24352,8 @@
       </c>
       <c r="G592" s="5" t="inlineStr">
         <is>
-          <t>As Chief of General Staff of the SPLA, Malong expanded or extended the conflict in South Sudan through breaches of the Cessation of Hostilities Agreement and breaches of the 2015 Agreement on the Resolution of the Conflict in South Sudan (ARCSS). He reportedly directed efforts to kill opposition leader Riek Machar. He ordered SPLA units to prevent the transport of humanitarian supplies. Under Malong’s leadership, the SPLA attacked civilians, schools and hospitals; forced the displacement of civilians; carried out enforced disappearances; arbitrarily detained civilians; and conducted acts of torture, and rape. He mobilized the Mathiang Anyoor Dinka tribal militia, which uses child soldiers. Under his leadership, the SPLA restricted UNMISS, the Joint Monitoring and Evaluation Commission (JMEC), and CTSAMM access to sites to investigate and document abuses.</t>
+          <t>As Chief of General Staff of the SPLA, Malong expanded or extended the conflict in South Sudan through breaches of the Cessation of Hostilities Agreement and breaches of the 2015 Agreement on the Resolution of the Conflict in South Sudan (ARCSS). He reportedly directed efforts to kill opposition leader Riek Machar. He ordered SPLA units to prevent the transport of humanitarian supplies. Under Malong’s leadership, the SPLA attacked civilians, schools and hospitals; forced the displacement of civilians; carried out enforced disappearances; arbitrarily detained civilians; and conducted acts of torture, and rape. He mobilized the Mathiang Anyoor Dinka tribal militia, which uses child soldiers. Under his leadership, the SPLA restricted UNMISS, the Joint Monitoring and Evaluation Commission (JMEC), and CTSAMM access to sites to investigate and document abuses.
+ INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H592" s="5" t="inlineStr">
@@ -24429,7 +24433,7 @@
       </c>
       <c r="G594" s="5" t="inlineStr">
         <is>
-          <t>Active in terrorist operations in Eastern Afghanistan. Collects money from drug traffickers. Member of the Taliban Supreme Council as at 2009. Family is originally from Neka District, Paktia Province, Afghanistan. Responsible for attack on Afghan parliamentarians in November 2007 in Baghlan; owns land in central Baghlan Province. Belongs to Zadran tribe. Height 185 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-47114</t>
+          <t>Active in terrorist operations in Eastern Afghanistan. Collects money from drug traffickers. Member of the Taliban Supreme Council as at 2009. Family is originally from Neka District, Paktia Province, Afghanistan. Responsible for attack on Afghan parliamentarians in November 2007 in Baghlan; owns land in central Baghlan Province. Belongs to Zadran tribe. Height 185 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H594" s="5" t="inlineStr">
@@ -24593,7 +24597,7 @@
       </c>
       <c r="G598" s="5" t="inlineStr">
         <is>
-          <t>Taliban Shadow Governor for Logar Province as of late 2012. Belongs to Sahak tribe (Ghilzai). Height 170 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25913</t>
+          <t>Taliban Shadow Governor for Logar Province as of late 2012. Belongs to Sahak tribe (Ghilzai). Height 170 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H598" s="5" t="inlineStr">
@@ -25085,7 +25089,7 @@
       </c>
       <c r="G610" s="5" t="inlineStr">
         <is>
-          <t>Missing left leg since 1996. Serious injury on his right foot. Height 168 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-316058</t>
+          <t>Missing left leg since 1996. Serious injury on his right foot. Height 168 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H610" s="5" t="inlineStr">
@@ -25253,7 +25257,7 @@
       </c>
       <c r="G614" s="5" t="inlineStr">
         <is>
-          <t>Taliban member responsible for Jawzjan Province in Northern Afghanistan until 2008. Involved in drug trafficking. Height 178 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25909</t>
+          <t>Taliban member responsible for Jawzjan Province in Northern Afghanistan until 2008. Involved in drug trafficking. Height 178 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H614" s="5" t="inlineStr">
@@ -25535,7 +25539,7 @@
       </c>
       <c r="G621" s="5" t="inlineStr">
         <is>
-          <t>Taliban member responsible for Nangarhar Province as at 2008. Until 7 Sep. 2007 he was also listed under number TAi.048. Height 175 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-47507</t>
+          <t>Taliban member responsible for Nangarhar Province as at 2008. Until 7 Sep. 2007 he was also listed under number TAi.048. Height 175 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H621" s="5" t="inlineStr">
@@ -25699,7 +25703,7 @@
       </c>
       <c r="G625" s="5" t="inlineStr">
         <is>
-          <t>Member of Taliban Supreme Council responsible for Takhar and Badakhshan provinces. Height 172 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-47175</t>
+          <t>Member of Taliban Supreme Council responsible for Takhar and Badakhshan provinces. Height 172 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H625" s="5" t="inlineStr">
@@ -25741,7 +25745,7 @@
       </c>
       <c r="G626" s="5" t="inlineStr">
         <is>
-          <t>Member of the Taliban Supreme Council. Believed to be in Afghanistan/Pakistan border area. Height 174 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25939</t>
+          <t>Member of the Taliban Supreme Council. Believed to be in Afghanistan/Pakistan border area. Height 174 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H626" s="5" t="inlineStr">
@@ -26027,7 +26031,7 @@
       </c>
       <c r="G633" s="5" t="inlineStr">
         <is>
-          <t>Deputy to Mullah Mohammed Omar (TAi.004). Height 165 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25960</t>
+          <t>Deputy to Mullah Mohammed Omar (TAi.004). Height 165 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H633" s="5" t="inlineStr">
@@ -26069,7 +26073,7 @@
       </c>
       <c r="G634" s="5" t="inlineStr">
         <is>
-          <t>Belongs to Nurzai tribe. Height 185 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25957</t>
+          <t>Belongs to Nurzai tribe. Height 185 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H634" s="5" t="inlineStr">
@@ -26397,7 +26401,7 @@
       </c>
       <c r="G642" s="5" t="inlineStr">
         <is>
-          <t>Cousin of Moulavi Noor Jalal. Grandfather’s name is Salam. Taliban member responsible for Laghman Province as of late 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-47312</t>
+          <t>Cousin of Moulavi Noor Jalal. Grandfather’s name is Salam. Taliban member responsible for Laghman Province as of late 2010. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H642" s="5" t="inlineStr">
@@ -26683,7 +26687,7 @@
       </c>
       <c r="G649" s="5" t="inlineStr">
         <is>
-          <t>Height 168 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25979</t>
+          <t>Height 168 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H649" s="5" t="inlineStr">
@@ -27057,7 +27061,7 @@
       </c>
       <c r="G658" s="5" t="inlineStr">
         <is>
-          <t>Belongs to Popalzai tribe. Height 176 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-25973</t>
+          <t>Belongs to Popalzai tribe. Height 176 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H658" s="5" t="inlineStr">
@@ -27751,7 +27755,7 @@
       </c>
       <c r="G675" s="5" t="inlineStr">
         <is>
-          <t>Member of Taliban Supreme Council and Head of Taliban Religious Committee. Belongs to Ahmadzai tribe. Height 175 cm or 180 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-26129</t>
+          <t>Member of Taliban Supreme Council and Head of Taliban Religious Committee. Belongs to Ahmadzai tribe. Height 175 cm or 180 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H675" s="5" t="inlineStr">
@@ -27793,7 +27797,7 @@
       </c>
       <c r="G676" s="5" t="inlineStr">
         <is>
-          <t>Reportedly deceased in 2001. Belonged to Kakar tribe</t>
+          <t>Reportedly deceased in 2001. Belonged to Kakar tribe INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H676" s="5" t="inlineStr">
@@ -27911,7 +27915,7 @@
       </c>
       <c r="G679" s="5" t="inlineStr">
         <is>
-          <t>Belongs to Ghilzai tribe. Height: 175 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2006-26140</t>
+          <t>Belongs to Ghilzai tribe. Height: 175 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H679" s="5" t="inlineStr">
@@ -27991,7 +27995,7 @@
       </c>
       <c r="G681" s="5" t="inlineStr">
         <is>
-          <t>Belongs to Hotak tribe. Height 169 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-306385</t>
+          <t>Belongs to Hotak tribe. Height 169 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H681" s="5" t="inlineStr">
@@ -28719,7 +28723,7 @@
       </c>
       <c r="G699" s="5" t="inlineStr">
         <is>
-          <t>Heading the Haqqani Network (TAe.012) as of late 2012. Son of Jalaluddin Haqqani (TAi.040). Belongs to Sultan Khel section, Zadran tribe of Garda Saray of Paktia province, Afghanistan. Height 187 cm or 180cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2007-44300</t>
+          <t>Heading the Haqqani Network (TAe.012) as of late 2012. Son of Jalaluddin Haqqani (TAi.040). Belongs to Sultan Khel section, Zadran tribe of Garda Saray of Paktia province, Afghanistan. Height 187 cm or 180cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H699" s="5" t="inlineStr">
@@ -29135,7 +29139,7 @@
       </c>
       <c r="G709" s="5" t="inlineStr">
         <is>
-          <t>Senior Taliban official with military and financial responsibilities as at 2011. Leader of the Taliban’s Military Council as of 2010. In 2008 and 2009, served as a Taliban finance officer and distributed money to Taliban commanders in Afghanistan/Pakistan border area. Height: 180 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals#2012-308182</t>
+          <t>Senior Taliban official with military and financial responsibilities as at 2011. Leader of the Taliban’s Military Council as of 2010. In 2008 and 2009, served as a Taliban finance officer and distributed money to Taliban commanders in Afghanistan/Pakistan border area. Height: 180 cm. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H709" s="5" t="inlineStr">
@@ -37320,7 +37324,7 @@
       <c r="F931" s="5" t="inlineStr"/>
       <c r="G931" s="5" t="inlineStr">
         <is>
-          <t>Headquarters was in Kandahar, Afghanistan as at 2001. Wafa was a component of Al-Qaida (QDe.004) in 2001. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2008-18095</t>
+          <t>Headquarters was in Kandahar, Afghanistan as at 2001. Wafa was a component of Al-Qaida (QDe.004) in 2001. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H931" s="5" t="inlineStr">
@@ -37464,7 +37468,7 @@
       <c r="F935" s="5" t="inlineStr"/>
       <c r="G935" s="5" t="inlineStr">
         <is>
-          <t>Its directors included Mahmood Sultan Bashir-Ud-Din (QDi.055). Banned in Pakistan. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2008-18090</t>
+          <t>Its directors included Mahmood Sultan Bashir-Ud-Din (QDi.055). Banned in Pakistan. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H935" s="5" t="inlineStr">
@@ -37502,7 +37506,7 @@
       <c r="F936" s="5" t="inlineStr"/>
       <c r="G936" s="5" t="inlineStr">
         <is>
-          <t>Associated with the Revival of Islamic Heritage Society (QDe.070). Abu Bakr al-Jaziri (QDi.058) served as finance chief of ASC. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2023-75320</t>
+          <t>Associated with the Revival of Islamic Heritage Society (QDe.070). Abu Bakr al-Jaziri (QDi.058) served as finance chief of ASC. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H936" s="5" t="inlineStr">
@@ -37798,7 +37802,7 @@
       <c r="F944" s="5" t="inlineStr"/>
       <c r="G944" s="5" t="inlineStr">
         <is>
-          <t>Banned in Pakistan as at 2010. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2013-17114</t>
+          <t>Banned in Pakistan as at 2010. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H944" s="5" t="inlineStr">
@@ -37984,7 +37988,7 @@
       <c r="F949" s="5" t="inlineStr"/>
       <c r="G949" s="5" t="inlineStr">
         <is>
-          <t>As at late 2025, it was not active and had no structures in Pakistan. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2013-46151</t>
+          <t>As at late 2025, it was not active and had no structures in Pakistan. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H949" s="5" t="inlineStr">
@@ -38488,7 +38492,7 @@
       <c r="F963" s="5" t="inlineStr"/>
       <c r="G963" s="5" t="inlineStr">
         <is>
-          <t>Founded and led by Najmiddin Kamolitdinovich Jalolov (reportedly deceased) and Suhayl Fatilloevich Buranov (reportedly deceased). Its activities are funded and coordinated by Al-Qaida. Associated with the Islamic Movement of Uzbekistan (QDe.010) and Emarat Kavkaz (QDe.131). Active in the Afghanistan/Pakistan border area, Central Asia, South Asia region and some European States. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2013-16764</t>
+          <t>Founded and led by Najmiddin Kamolitdinovich Jalolov (reportedly deceased) and Suhayl Fatilloevich Buranov (reportedly deceased). Its activities are funded and coordinated by Al-Qaida. Associated with the Islamic Movement of Uzbekistan (QDe.010) and Emarat Kavkaz (QDe.131). Active in the Afghanistan/Pakistan border area, Central Asia, South Asia region and some European States. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H963" s="5" t="inlineStr">
@@ -38602,7 +38606,7 @@
       <c r="F966" s="5" t="inlineStr"/>
       <c r="G966" s="5" t="inlineStr">
         <is>
-          <t>AQAP is a regional affiliate of Al-Qaida (QDe.004) and an armed group operating primarily in Arabian Peninsula. Location: Yemen. Alternative location: Saudi Arabia (2004 – 2006). Formed in Jan. 2009 when Al-Qaida in Yemen combined with Saudi Arabian Al-Qaida operatives. Leader of AQAP is Sa'ad bin Atef al-Awlaki. Ansar al-Shari’a was formed in early 2011 by AQAP and has taken responsibility for multiple attacks in Yemen against both government and civilian targets. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2013-17222</t>
+          <t>AQAP is a regional affiliate of Al-Qaida (QDe.004) and an armed group operating primarily in Arabian Peninsula. Location: Yemen. Alternative location: Saudi Arabia (2004 – 2006). Formed in Jan. 2009 when Al-Qaida in Yemen combined with Saudi Arabian Al-Qaida operatives. Leader of AQAP is Sa'ad bin Atef al-Awlaki. Ansar al-Shari’a was formed in early 2011 by AQAP and has taken responsibility for multiple attacks in Yemen against both government and civilian targets. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H966" s="5" t="inlineStr">
@@ -38784,7 +38788,7 @@
       <c r="F971" s="5" t="inlineStr"/>
       <c r="G971" s="5" t="inlineStr">
         <is>
-          <t>Associated with The Organization of Al-Qaida in the Islamic Maghreb, (QDe.014), Al Mourabitoun (QDe.141), and Mokhtar Belmokhtar (QDi.136). Active in the Sahel/Sahara region. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2013-17116</t>
+          <t>Associated with The Organization of Al-Qaida in the Islamic Maghreb, (QDe.014), Al Mourabitoun (QDe.141), and Mokhtar Belmokhtar (QDi.136). Active in the Sahel/Sahara region. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H971" s="5" t="inlineStr">
@@ -39768,7 +39772,7 @@
       <c r="F997" s="5" t="inlineStr"/>
       <c r="G997" s="5" t="inlineStr">
         <is>
-          <t>Islamic State of Iraq and the Levant - Khorasan (ISIL - K) was formed on January 10, 2015 by a former Tehrik-e Taliban Pakistan (TTP) (QDe.132) commander and was established by former Taliban faction commanders who swore an oath of allegiance to the Islamic State of Iraq and the Levant (listed as Al-Qaida in Iraq (QDe.115)). ISIL – K has claimed responsibility for numerous attacks in both Afghanistan and Pakistan. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities#2019-54448</t>
+          <t>Islamic State of Iraq and the Levant - Khorasan (ISIL - K) was formed on January 10, 2015 by a former Tehrik-e Taliban Pakistan (TTP) (QDe.132) commander and was established by former Taliban faction commanders who swore an oath of allegiance to the Islamic State of Iraq and the Levant (listed as Al-Qaida in Iraq (QDe.115)). ISIL – K has claimed responsibility for numerous attacks in both Afghanistan and Pakistan. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H997" s="5" t="inlineStr">
@@ -40023,12 +40027,12 @@
       </c>
       <c r="D1004" s="5" t="inlineStr">
         <is>
-          <t>KHATIBA AL-TAWHID WAL-JIHAD (KTJ)</t>
+          <t>KHATIBA JAMA`AT AL-TAWHID WAL-JIHAD (KTJ)</t>
         </is>
       </c>
       <c r="E1004" s="5" t="inlineStr">
         <is>
-          <t>JANNAT OSHIKLARI ; Jama`at al-Tawhid wal-Jihad ; JANNAT OSHIKLARI</t>
+          <t>JANNAT OSHIKLARI ; Jama`at al-Tawhid wal-Jihad ; Katiba al-Tawhid wal-Jihad</t>
         </is>
       </c>
       <c r="F1004" s="5" t="inlineStr"/>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29T02:26:43+00:00</t>
+          <t>2026-09-30T01:45:59+00:00</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="B917" s="5" t="inlineStr">
         <is>
-          <t>6909568</t>
+          <t>6909645</t>
         </is>
       </c>
       <c r="C917" s="5" t="inlineStr">

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-30T01:45:59+00:00</t>
+          <t>2026-10-01T01:44:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-01T01:44:17+00:00</t>
+          <t>2026-10-02T01:54:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02T01:54:35+00:00</t>
+          <t>2026-10-03T01:37:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-03T01:37:25+00:00</t>
+          <t>2026-10-04T02:17:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-04T02:17:50+00:00</t>
+          <t>2026-10-05T01:26:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-05T01:26:27+00:00</t>
+          <t>2026-10-06T02:37:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-07T01:55:28+00:00</t>
+          <t>2026-10-08T02:23:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08T02:23:36+00:00</t>
+          <t>2026-10-09T02:41:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-09T02:41:00+00:00</t>
+          <t>2026-10-10T02:01:13+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T02:01:13+00:00</t>
+          <t>2026-10-10T09:15:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T09:15:53+00:00</t>
+          <t>2026-10-10T16:03:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T16:03:48+00:00</t>
+          <t>2026-10-10T22:08:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T22:08:12+00:00</t>
+          <t>2026-10-11T01:26:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T01:26:19+00:00</t>
+          <t>2026-10-11T09:32:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T09:32:56+00:00</t>
+          <t>2026-10-11T16:29:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T16:29:16+00:00</t>
+          <t>2026-10-11T22:36:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T22:36:53+00:00</t>
+          <t>2026-10-12T01:56:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T01:56:36+00:00</t>
+          <t>2026-10-12T10:02:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T10:02:58+00:00</t>
+          <t>2026-10-12T20:05:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T20:05:03+00:00</t>
+          <t>2026-10-13T03:18:18+00:00</t>
         </is>
       </c>
     </row>
@@ -36656,8 +36656,7 @@
       <c r="F913" s="5" t="inlineStr"/>
       <c r="G913" s="5" t="inlineStr">
         <is>
-          <t>Ship manager and commercial manager of the YUK TUNG, which conducted
-ship-to-ship transfer of refined petroleum product. IMO number: 5987860.</t>
+          <t>Ship manager and commercial manager of the YUK TUNG, which conducted ship-to-ship transfer of refined petroleum product. IMO number: 5987860.</t>
         </is>
       </c>
       <c r="H913" s="5" t="inlineStr">

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T03:18:18+00:00</t>
+          <t>2026-10-13T14:43:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T14:43:33+00:00</t>
+          <t>2026-10-13T20:28:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T20:28:27+00:00</t>
+          <t>2026-10-14T01:30:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T01:30:45+00:00</t>
+          <t>2026-10-14T08:15:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T08:15:38+00:00</t>
+          <t>2026-10-14T15:40:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T15:40:04+00:00</t>
+          <t>2026-10-14T22:00:14+00:00</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>In 2016, Ch’oe So’k-min was the deputy representative at the Foreign Trade Bank branch office in that overseas location.  He has been associated with cash transfers from that overseas Foreign Trade Bank office to banks affiliated with North Korean special organizations and Reconnaissance General Bureau operatives located overseas in an effort to evade sanctions. Gender: male.in response to the DPRK test of an ICBM on 28 November 2017</t>
+          <t>In 2016, Ch’oe So’k-min was the deputy representative at the Foreign Trade Bank branch office in that overseas location. He has been associated with cash transfers from that overseas Foreign Trade Bank office to banks affiliated with North Korean special organizations and Reconnaissance General Bureau operatives located overseas in an effort to evade sanctions. Gender: male.</t>
         </is>
       </c>
       <c r="H256" s="5" t="inlineStr">

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T22:00:14+00:00</t>
+          <t>2026-10-15T01:08:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T01:08:29+00:00</t>
+          <t>2026-10-15T07:53:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T07:53:14+00:00</t>
+          <t>2026-10-15T15:26:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T15:26:11+00:00</t>
+          <t>2026-10-15T21:54:01+00:00</t>
         </is>
       </c>
     </row>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="G334" s="5" t="inlineStr">
         <is>
-          <t>Arrested on 28 Nov. 2001 and found guilty in Germany of being an accessory to murder and of membership in a terrorist organization and sentenced to 15 years of imprisonment on 8 Jan. 2007. Father's name is Brahim Brik. Mother's name is Habiba Abbes INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Arrested on 28 Nov. 2001 and found guilty in Germany of being an accessory to murder and of membership in a terrorist organization and sentenced to 15 years of imprisonment on 8 Jan. 2007. Deported from Germany to Morocco in October 2018. Father's name is Brahim Brik. Mother's name is Habiba Abbes. Photo available for inclusion in the INTERPOL-UN Security Council Special Notice. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H334" s="5" t="inlineStr">
@@ -22105,7 +22105,7 @@
       </c>
       <c r="G537" s="5" t="inlineStr">
         <is>
-          <t>Leader of Tehrik-e Taliban Pakistan (TTP) (QDe.132) following the death of former TTP leader Maulana Fazlullah (QDi.352) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Leader of Tehrik-e Taliban Pakistan (TTP) (QDe.132) following the death of former TTP leader Maulana Fazlullah (QDi.352). Photo available for inclusion in the INTERPOL-UN Security Council Special Notice.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H537" s="5" t="inlineStr">
@@ -38677,7 +38677,7 @@
       <c r="F968" s="5" t="inlineStr"/>
       <c r="G968" s="5" t="inlineStr">
         <is>
-          <t>Tehrik-e Taliban is based in the tribal areas along the Afghanistan/Pakistan border. Formed in 2007, its leader is Maulana Fazlullah (QDi.352) INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
+          <t>Tehrik-e Taliban is based in the tribal areas along the Afghanistan/Pakistan border. Formed in 2007, its leader is Noor Wali Mehsud (QDi.427). INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Entities</t>
         </is>
       </c>
       <c r="H968" s="5" t="inlineStr">

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T21:54:01+00:00</t>
+          <t>2026-10-16T00:55:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T00:55:56+00:00</t>
+          <t>2026-10-16T07:45:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T07:45:02+00:00</t>
+          <t>2026-10-16T15:06:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T15:06:02+00:00</t>
+          <t>2026-10-16T21:52:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T21:52:01+00:00</t>
+          <t>2026-10-17T00:56:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T00:56:12+00:00</t>
+          <t>2026-10-17T07:22:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T07:22:19+00:00</t>
+          <t>2026-10-17T14:00:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T14:00:52+00:00</t>
+          <t>2026-10-17T17:40:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T17:40:37+00:00</t>
+          <t>2026-10-17T21:10:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T21:10:42+00:00</t>
+          <t>2026-10-18T00:31:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T00:31:30+00:00</t>
+          <t>2026-10-18T07:36:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T07:36:31+00:00</t>
+          <t>2026-10-18T14:14:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T14:14:18+00:00</t>
+          <t>2026-10-18T17:42:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T17:42:40+00:00</t>
+          <t>2026-10-18T21:12:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T21:12:46+00:00</t>
+          <t>2026-10-19T00:38:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T00:38:08+00:00</t>
+          <t>2026-10-19T08:19:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T08:19:26+00:00</t>
+          <t>2026-10-19T17:17:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T17:17:36+00:00</t>
+          <t>2026-10-19T22:42:59+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T22:42:59+00:00</t>
+          <t>2026-10-20T01:23:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T01:23:16+00:00</t>
+          <t>2026-10-20T08:04:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T08:04:14+00:00</t>
+          <t>2026-10-20T15:30:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T15:30:37+00:00</t>
+          <t>2026-10-20T22:01:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T22:01:00+00:00</t>
+          <t>2026-10-21T01:10:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T01:10:03+00:00</t>
+          <t>2026-10-21T08:09:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T08:09:42+00:00</t>
+          <t>2026-10-21T15:46:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T15:46:43+00:00</t>
+          <t>2026-10-21T22:03:34+00:00</t>
         </is>
       </c>
     </row>
@@ -34340,15 +34340,7 @@
       <c r="F849" s="5" t="inlineStr"/>
       <c r="G849" s="5" t="inlineStr">
         <is>
-          <t>The Korea Heungjin Trading Company is used by KOMID for trading purposes.
-We suspect it has been involved in supplying missile-related goods to Iran’s Shahid
-Hemmat Industrial Group (SHIG). Heungjin has been associated with KOMID, and, more
-specifically, KOMID’s procurement office. Heungjin has been used to procure an advanced
-digital controller with applications in missile design. KOMID was designated by the
-Committee in April 2009 and is the DPRK’s primary arms dealer and main exporter of goods
-and equipment related to ballistic missiles and conventional weapons. The Security
-Council designated SHIG in resolution 1737 (2006) as an entity involved in Iran’s
-ballistic missile programme.</t>
+          <t>The Korea Heungjin Trading Company is used by KOMID for trading purposes. We suspect it has been involved in supplying missile-related goods to Iran’s Shahid Hemmat Industrial Group (SHIG). Heungjin has been associated with KOMID, and, more specifically, KOMID’s procurement office. Heungjin has been used to procure an advanced digital controller with applications in missile design. KOMID was designated by the Committee in April 2009 and is the DPRK’s primary arms dealer and main exporter of goods and equipment related to ballistic missiles and conventional weapons. The Security Council designated SHIG in resolution 1737 (2006) as an entity involved in Iran’s ballistic missile programme.</t>
         </is>
       </c>
       <c r="H849" s="5" t="inlineStr">

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T22:03:34+00:00</t>
+          <t>2026-10-22T01:06:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T01:06:48+00:00</t>
+          <t>2026-10-22T08:09:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T08:09:47+00:00</t>
+          <t>2026-10-22T15:45:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T15:45:46+00:00</t>
+          <t>2026-10-22T22:01:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T22:01:00+00:00</t>
+          <t>2026-10-23T01:07:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T01:07:48+00:00</t>
+          <t>2026-10-23T08:08:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T08:08:27+00:00</t>
+          <t>2026-10-23T15:33:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T15:33:55+00:00</t>
+          <t>2026-10-23T21:47:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T21:47:48+00:00</t>
+          <t>2026-10-24T01:16:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T01:16:53+00:00</t>
+          <t>2026-10-24T07:47:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T07:47:10+00:00</t>
+          <t>2026-10-24T09:09:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T09:09:36+00:00</t>
+          <t>2026-10-24T14:12:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T14:12:02+00:00</t>
+          <t>2026-10-24T15:22:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T15:22:41+00:00</t>
+          <t>2026-10-24T17:44:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T21:20:38+00:00</t>
+          <t>2026-10-25T00:42:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T00:42:28+00:00</t>
+          <t>2026-10-25T07:57:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T07:57:15+00:00</t>
+          <t>2026-10-25T14:42:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T14:42:45+00:00</t>
+          <t>2026-10-25T18:00:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T18:00:25+00:00</t>
+          <t>2026-10-25T21:25:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T21:25:27+00:00</t>
+          <t>2026-10-26T00:56:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T00:56:48+00:00</t>
+          <t>2026-10-26T08:28:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T08:28:28+00:00</t>
+          <t>2026-10-26T17:04:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T17:04:48+00:00</t>
+          <t>2026-10-26T22:57:06+00:00</t>
         </is>
       </c>
     </row>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="G461" s="5" t="inlineStr">
         <is>
-          <t>French terrorist fighter who travelled to Syria and joined Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115). Active in radicalizing and propagating Al-Qaida’s (QDe.004) ideology through the Internet. Incites violent activities against France. French arrest warrant issued on 12 Jun. 2015 by a magistrate of the anti-terrorism division of the Prosecutor’s Office in Paris for her participation in a terrorist criminal association INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>French terrorist fighter who travelled to Syria and joined Islamic State in Iraq and the Levant, listed as Al-Qaida in Iraq (AQI) (QDe.115). Active in radicalizing and propagating Al-Qaida’s (QDe.004) ideology through the Internet. Incites violent activities against France. Currently detained in France. Gender: Female. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H461" s="5" t="inlineStr">
@@ -19023,7 +19023,7 @@
       </c>
       <c r="E463" s="5" t="inlineStr">
         <is>
-          <t>Omsen ; Oumar Omsen</t>
+          <t>Omsen ; Omar Omsen</t>
         </is>
       </c>
       <c r="F463" s="5" t="inlineStr">
@@ -19033,7 +19033,7 @@
       </c>
       <c r="G463" s="5" t="inlineStr">
         <is>
-          <t>A leader of an armed group linked to Al-Nusrah Front for the People of the Levant (formerly listed) and a key facilitator for a Syrian foreign terrorist fighter network. Active in terrorist propaganda through the Internet INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>A leader of an armed group linked to Al-Qaida (QDe.004) and Al-Nusrah Front for the People of the Levant (formerly listed) and a key facilitator for a network of foreign terrorist fighters travelling to Syria. Active in terrorist propaganda through the Internet. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H463" s="5" t="inlineStr">
@@ -20185,7 +20185,11 @@
           <t>PETER CHERIF</t>
         </is>
       </c>
-      <c r="E491" s="5" t="inlineStr"/>
+      <c r="E491" s="5" t="inlineStr">
+        <is>
+          <t>Abou Hamza</t>
+        </is>
+      </c>
       <c r="F491" s="5" t="inlineStr">
         <is>
           <t>France</t>
@@ -20193,7 +20197,7 @@
       </c>
       <c r="G491" s="5" t="inlineStr">
         <is>
-          <t>Member of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Convicted in absentia to five years in prison in France in 2012. Wanted by French authorities as of 2015. Sentenced to life imprisonment by a French court on 3 October 2024.  INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
+          <t>Member of Al-Qaida in the Arabian Peninsula (AQAP) (QDe.129). Convicted in absentia to five years in prison in France in 2012, and then sentenced to life imprisonment by a French court on 3 October 2024 for his involvement in a terrorist organisation. INTERPOL-UN Security Council Special Notice:https://www.interpol.int/en/How-we-work/Notices/View-UN-Notices-Individuals</t>
         </is>
       </c>
       <c r="H491" s="5" t="inlineStr">

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T22:57:06+00:00</t>
+          <t>2026-10-27T01:44:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T01:44:38+00:00</t>
+          <t>2026-10-27T01:47:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T01:47:48+00:00</t>
+          <t>2026-10-27T08:31:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T08:31:43+00:00</t>
+          <t>2026-10-27T16:08:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T16:08:03+00:00</t>
+          <t>2026-10-27T22:46:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T22:46:37+00:00</t>
+          <t>2026-10-28T01:56:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T01:56:03+00:00</t>
+          <t>2026-10-28T09:09:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T09:09:50+00:00</t>
+          <t>2026-10-28T16:55:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T16:55:25+00:00</t>
+          <t>2026-10-28T22:55:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:55:28+00:00</t>
+          <t>2026-10-29T02:00:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T02:00:36+00:00</t>
+          <t>2026-10-29T06:40:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T06:40:56+00:00</t>
+          <t>2026-10-29T09:09:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T09:09:15+00:00</t>
+          <t>2026-10-29T17:13:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T17:13:10+00:00</t>
+          <t>2026-10-29T23:03:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T23:03:35+00:00</t>
+          <t>2026-10-30T02:16:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T02:16:53+00:00</t>
+          <t>2026-10-30T09:20:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T09:20:08+00:00</t>
+          <t>2026-10-30T16:54:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T16:54:12+00:00</t>
+          <t>2026-10-30T22:44:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/un-consolidated.xlsx
+++ b/public/downloads/un-consolidated.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T22:44:41+00:00</t>
+          <t>2026-10-31T01:56:06+00:00</t>
         </is>
       </c>
     </row>
